--- a/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_72mo.xlsx
+++ b/docs/payment-schedule-templates/Payment Schedules - Customer Portal/Collection_Schedule_Template_72mo.xlsx
@@ -1247,20 +1247,55 @@
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="14">
-      <c r="A2" s="20" t="n"/>
-      <c r="B2" s="20" t="n"/>
-      <c r="C2" s="20" t="n"/>
-      <c r="D2" s="20" t="n"/>
-      <c r="E2" s="20" t="n"/>
-      <c r="F2" s="20" t="n"/>
-      <c r="G2" s="21" t="n"/>
-      <c r="H2" s="21" t="n"/>
-      <c r="I2" s="21" t="n"/>
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>{{########}}</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Nyandoro</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>+17785808657</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>alex@michaeltenable.com</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Internal Tester</t>
+        </is>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>120000</v>
+      </c>
       <c r="J2" s="22" t="n">
         <v>72</v>
       </c>
-      <c r="K2" s="21" t="n"/>
-      <c r="L2" s="23" t="n"/>
+      <c r="K2" s="21">
+        <f>IF(J2=0,"",ROUND((I2-H2)/J2,2))</f>
+        <v/>
+      </c>
+      <c r="L2" s="23" t="n">
+        <v>46147</v>
+      </c>
       <c r="M2" s="21" t="n"/>
       <c r="N2" s="21" t="n"/>
       <c r="O2" s="21" t="n"/>
@@ -1335,15 +1370,15 @@
       <c r="CF2" s="21" t="n"/>
       <c r="CG2" s="21" t="n"/>
       <c r="CH2" s="24">
-        <f>SUM(M2:CF2)</f>
+        <f>H2+SUM(M2:CF2)</f>
         <v/>
       </c>
       <c r="CI2" s="24">
-        <f>I2-CH2</f>
+        <f>I2-H2-SUM(M2:CF2)</f>
         <v/>
       </c>
       <c r="CJ2" s="25">
-        <f>IF(I2=0,"",CH2/I2)</f>
+        <f>IF(I2=0,"",(H2+SUM(M2:CF2))/I2)</f>
         <v/>
       </c>
       <c r="CK2" s="26" t="n"/>
@@ -1444,15 +1479,15 @@
       <c r="CF3" s="21" t="n"/>
       <c r="CG3" s="21" t="n"/>
       <c r="CH3" s="24">
-        <f>SUM(M3:CF3)</f>
+        <f>H3+SUM(M3:CF3)</f>
         <v/>
       </c>
       <c r="CI3" s="24">
-        <f>I3-CH3</f>
+        <f>I3-H3-SUM(M3:CF3)</f>
         <v/>
       </c>
       <c r="CJ3" s="25">
-        <f>IF(I3=0,"",CH3/I3)</f>
+        <f>IF(I3=0,"",(H3+SUM(M3:CF3))/I3)</f>
         <v/>
       </c>
       <c r="CK3" s="26" t="n"/>
@@ -1553,15 +1588,15 @@
       <c r="CF4" s="21" t="n"/>
       <c r="CG4" s="21" t="n"/>
       <c r="CH4" s="24">
-        <f>SUM(M4:CF4)</f>
+        <f>H4+SUM(M4:CF4)</f>
         <v/>
       </c>
       <c r="CI4" s="24">
-        <f>I4-CH4</f>
+        <f>I4-H4-SUM(M4:CF4)</f>
         <v/>
       </c>
       <c r="CJ4" s="25">
-        <f>IF(I4=0,"",CH4/I4)</f>
+        <f>IF(I4=0,"",(H4+SUM(M4:CF4))/I4)</f>
         <v/>
       </c>
       <c r="CK4" s="26" t="n"/>
@@ -1662,15 +1697,15 @@
       <c r="CF5" s="21" t="n"/>
       <c r="CG5" s="21" t="n"/>
       <c r="CH5" s="24">
-        <f>SUM(M5:CF5)</f>
+        <f>H5+SUM(M5:CF5)</f>
         <v/>
       </c>
       <c r="CI5" s="24">
-        <f>I5-CH5</f>
+        <f>I5-H5-SUM(M5:CF5)</f>
         <v/>
       </c>
       <c r="CJ5" s="25">
-        <f>IF(I5=0,"",CH5/I5)</f>
+        <f>IF(I5=0,"",(H5+SUM(M5:CF5))/I5)</f>
         <v/>
       </c>
       <c r="CK5" s="26" t="n"/>
@@ -1771,15 +1806,15 @@
       <c r="CF6" s="21" t="n"/>
       <c r="CG6" s="21" t="n"/>
       <c r="CH6" s="24">
-        <f>SUM(M6:CF6)</f>
+        <f>H6+SUM(M6:CF6)</f>
         <v/>
       </c>
       <c r="CI6" s="24">
-        <f>I6-CH6</f>
+        <f>I6-H6-SUM(M6:CF6)</f>
         <v/>
       </c>
       <c r="CJ6" s="25">
-        <f>IF(I6=0,"",CH6/I6)</f>
+        <f>IF(I6=0,"",(H6+SUM(M6:CF6))/I6)</f>
         <v/>
       </c>
       <c r="CK6" s="26" t="n"/>
@@ -1880,15 +1915,15 @@
       <c r="CF7" s="21" t="n"/>
       <c r="CG7" s="21" t="n"/>
       <c r="CH7" s="24">
-        <f>SUM(M7:CF7)</f>
+        <f>H7+SUM(M7:CF7)</f>
         <v/>
       </c>
       <c r="CI7" s="24">
-        <f>I7-CH7</f>
+        <f>I7-H7-SUM(M7:CF7)</f>
         <v/>
       </c>
       <c r="CJ7" s="25">
-        <f>IF(I7=0,"",CH7/I7)</f>
+        <f>IF(I7=0,"",(H7+SUM(M7:CF7))/I7)</f>
         <v/>
       </c>
       <c r="CK7" s="26" t="n"/>
@@ -1989,15 +2024,15 @@
       <c r="CF8" s="21" t="n"/>
       <c r="CG8" s="21" t="n"/>
       <c r="CH8" s="24">
-        <f>SUM(M8:CF8)</f>
+        <f>H8+SUM(M8:CF8)</f>
         <v/>
       </c>
       <c r="CI8" s="24">
-        <f>I8-CH8</f>
+        <f>I8-H8-SUM(M8:CF8)</f>
         <v/>
       </c>
       <c r="CJ8" s="25">
-        <f>IF(I8=0,"",CH8/I8)</f>
+        <f>IF(I8=0,"",(H8+SUM(M8:CF8))/I8)</f>
         <v/>
       </c>
       <c r="CK8" s="26" t="n"/>
@@ -2098,15 +2133,15 @@
       <c r="CF9" s="21" t="n"/>
       <c r="CG9" s="21" t="n"/>
       <c r="CH9" s="24">
-        <f>SUM(M9:CF9)</f>
+        <f>H9+SUM(M9:CF9)</f>
         <v/>
       </c>
       <c r="CI9" s="24">
-        <f>I9-CH9</f>
+        <f>I9-H9-SUM(M9:CF9)</f>
         <v/>
       </c>
       <c r="CJ9" s="25">
-        <f>IF(I9=0,"",CH9/I9)</f>
+        <f>IF(I9=0,"",(H9+SUM(M9:CF9))/I9)</f>
         <v/>
       </c>
       <c r="CK9" s="26" t="n"/>
@@ -2207,15 +2242,15 @@
       <c r="CF10" s="21" t="n"/>
       <c r="CG10" s="21" t="n"/>
       <c r="CH10" s="24">
-        <f>SUM(M10:CF10)</f>
+        <f>H10+SUM(M10:CF10)</f>
         <v/>
       </c>
       <c r="CI10" s="24">
-        <f>I10-CH10</f>
+        <f>I10-H10-SUM(M10:CF10)</f>
         <v/>
       </c>
       <c r="CJ10" s="25">
-        <f>IF(I10=0,"",CH10/I10)</f>
+        <f>IF(I10=0,"",(H10+SUM(M10:CF10))/I10)</f>
         <v/>
       </c>
       <c r="CK10" s="26" t="n"/>
@@ -2316,15 +2351,15 @@
       <c r="CF11" s="21" t="n"/>
       <c r="CG11" s="21" t="n"/>
       <c r="CH11" s="24">
-        <f>SUM(M11:CF11)</f>
+        <f>H11+SUM(M11:CF11)</f>
         <v/>
       </c>
       <c r="CI11" s="24">
-        <f>I11-CH11</f>
+        <f>I11-H11-SUM(M11:CF11)</f>
         <v/>
       </c>
       <c r="CJ11" s="25">
-        <f>IF(I11=0,"",CH11/I11)</f>
+        <f>IF(I11=0,"",(H11+SUM(M11:CF11))/I11)</f>
         <v/>
       </c>
       <c r="CK11" s="26" t="n"/>
@@ -2425,15 +2460,15 @@
       <c r="CF12" s="21" t="n"/>
       <c r="CG12" s="21" t="n"/>
       <c r="CH12" s="24">
-        <f>SUM(M12:CF12)</f>
+        <f>H12+SUM(M12:CF12)</f>
         <v/>
       </c>
       <c r="CI12" s="24">
-        <f>I12-CH12</f>
+        <f>I12-H12-SUM(M12:CF12)</f>
         <v/>
       </c>
       <c r="CJ12" s="25">
-        <f>IF(I12=0,"",CH12/I12)</f>
+        <f>IF(I12=0,"",(H12+SUM(M12:CF12))/I12)</f>
         <v/>
       </c>
       <c r="CK12" s="26" t="n"/>
@@ -2534,15 +2569,15 @@
       <c r="CF13" s="21" t="n"/>
       <c r="CG13" s="21" t="n"/>
       <c r="CH13" s="24">
-        <f>SUM(M13:CF13)</f>
+        <f>H13+SUM(M13:CF13)</f>
         <v/>
       </c>
       <c r="CI13" s="24">
-        <f>I13-CH13</f>
+        <f>I13-H13-SUM(M13:CF13)</f>
         <v/>
       </c>
       <c r="CJ13" s="25">
-        <f>IF(I13=0,"",CH13/I13)</f>
+        <f>IF(I13=0,"",(H13+SUM(M13:CF13))/I13)</f>
         <v/>
       </c>
       <c r="CK13" s="26" t="n"/>
@@ -2643,15 +2678,15 @@
       <c r="CF14" s="21" t="n"/>
       <c r="CG14" s="21" t="n"/>
       <c r="CH14" s="24">
-        <f>SUM(M14:CF14)</f>
+        <f>H14+SUM(M14:CF14)</f>
         <v/>
       </c>
       <c r="CI14" s="24">
-        <f>I14-CH14</f>
+        <f>I14-H14-SUM(M14:CF14)</f>
         <v/>
       </c>
       <c r="CJ14" s="25">
-        <f>IF(I14=0,"",CH14/I14)</f>
+        <f>IF(I14=0,"",(H14+SUM(M14:CF14))/I14)</f>
         <v/>
       </c>
       <c r="CK14" s="26" t="n"/>
@@ -2752,15 +2787,15 @@
       <c r="CF15" s="21" t="n"/>
       <c r="CG15" s="21" t="n"/>
       <c r="CH15" s="24">
-        <f>SUM(M15:CF15)</f>
+        <f>H15+SUM(M15:CF15)</f>
         <v/>
       </c>
       <c r="CI15" s="24">
-        <f>I15-CH15</f>
+        <f>I15-H15-SUM(M15:CF15)</f>
         <v/>
       </c>
       <c r="CJ15" s="25">
-        <f>IF(I15=0,"",CH15/I15)</f>
+        <f>IF(I15=0,"",(H15+SUM(M15:CF15))/I15)</f>
         <v/>
       </c>
       <c r="CK15" s="26" t="n"/>
@@ -2861,15 +2896,15 @@
       <c r="CF16" s="21" t="n"/>
       <c r="CG16" s="21" t="n"/>
       <c r="CH16" s="24">
-        <f>SUM(M16:CF16)</f>
+        <f>H16+SUM(M16:CF16)</f>
         <v/>
       </c>
       <c r="CI16" s="24">
-        <f>I16-CH16</f>
+        <f>I16-H16-SUM(M16:CF16)</f>
         <v/>
       </c>
       <c r="CJ16" s="25">
-        <f>IF(I16=0,"",CH16/I16)</f>
+        <f>IF(I16=0,"",(H16+SUM(M16:CF16))/I16)</f>
         <v/>
       </c>
       <c r="CK16" s="26" t="n"/>
@@ -2970,15 +3005,15 @@
       <c r="CF17" s="21" t="n"/>
       <c r="CG17" s="21" t="n"/>
       <c r="CH17" s="24">
-        <f>SUM(M17:CF17)</f>
+        <f>H17+SUM(M17:CF17)</f>
         <v/>
       </c>
       <c r="CI17" s="24">
-        <f>I17-CH17</f>
+        <f>I17-H17-SUM(M17:CF17)</f>
         <v/>
       </c>
       <c r="CJ17" s="25">
-        <f>IF(I17=0,"",CH17/I17)</f>
+        <f>IF(I17=0,"",(H17+SUM(M17:CF17))/I17)</f>
         <v/>
       </c>
       <c r="CK17" s="26" t="n"/>
@@ -3079,15 +3114,15 @@
       <c r="CF18" s="21" t="n"/>
       <c r="CG18" s="21" t="n"/>
       <c r="CH18" s="24">
-        <f>SUM(M18:CF18)</f>
+        <f>H18+SUM(M18:CF18)</f>
         <v/>
       </c>
       <c r="CI18" s="24">
-        <f>I18-CH18</f>
+        <f>I18-H18-SUM(M18:CF18)</f>
         <v/>
       </c>
       <c r="CJ18" s="25">
-        <f>IF(I18=0,"",CH18/I18)</f>
+        <f>IF(I18=0,"",(H18+SUM(M18:CF18))/I18)</f>
         <v/>
       </c>
       <c r="CK18" s="26" t="n"/>
@@ -3188,15 +3223,15 @@
       <c r="CF19" s="21" t="n"/>
       <c r="CG19" s="21" t="n"/>
       <c r="CH19" s="24">
-        <f>SUM(M19:CF19)</f>
+        <f>H19+SUM(M19:CF19)</f>
         <v/>
       </c>
       <c r="CI19" s="24">
-        <f>I19-CH19</f>
+        <f>I19-H19-SUM(M19:CF19)</f>
         <v/>
       </c>
       <c r="CJ19" s="25">
-        <f>IF(I19=0,"",CH19/I19)</f>
+        <f>IF(I19=0,"",(H19+SUM(M19:CF19))/I19)</f>
         <v/>
       </c>
       <c r="CK19" s="26" t="n"/>
@@ -3297,15 +3332,15 @@
       <c r="CF20" s="21" t="n"/>
       <c r="CG20" s="21" t="n"/>
       <c r="CH20" s="24">
-        <f>SUM(M20:CF20)</f>
+        <f>H20+SUM(M20:CF20)</f>
         <v/>
       </c>
       <c r="CI20" s="24">
-        <f>I20-CH20</f>
+        <f>I20-H20-SUM(M20:CF20)</f>
         <v/>
       </c>
       <c r="CJ20" s="25">
-        <f>IF(I20=0,"",CH20/I20)</f>
+        <f>IF(I20=0,"",(H20+SUM(M20:CF20))/I20)</f>
         <v/>
       </c>
       <c r="CK20" s="26" t="n"/>
@@ -3406,15 +3441,15 @@
       <c r="CF21" s="21" t="n"/>
       <c r="CG21" s="21" t="n"/>
       <c r="CH21" s="24">
-        <f>SUM(M21:CF21)</f>
+        <f>H21+SUM(M21:CF21)</f>
         <v/>
       </c>
       <c r="CI21" s="24">
-        <f>I21-CH21</f>
+        <f>I21-H21-SUM(M21:CF21)</f>
         <v/>
       </c>
       <c r="CJ21" s="25">
-        <f>IF(I21=0,"",CH21/I21)</f>
+        <f>IF(I21=0,"",(H21+SUM(M21:CF21))/I21)</f>
         <v/>
       </c>
       <c r="CK21" s="26" t="n"/>
@@ -3515,15 +3550,15 @@
       <c r="CF22" s="21" t="n"/>
       <c r="CG22" s="21" t="n"/>
       <c r="CH22" s="24">
-        <f>SUM(M22:CF22)</f>
+        <f>H22+SUM(M22:CF22)</f>
         <v/>
       </c>
       <c r="CI22" s="24">
-        <f>I22-CH22</f>
+        <f>I22-H22-SUM(M22:CF22)</f>
         <v/>
       </c>
       <c r="CJ22" s="25">
-        <f>IF(I22=0,"",CH22/I22)</f>
+        <f>IF(I22=0,"",(H22+SUM(M22:CF22))/I22)</f>
         <v/>
       </c>
       <c r="CK22" s="26" t="n"/>
@@ -3624,15 +3659,15 @@
       <c r="CF23" s="21" t="n"/>
       <c r="CG23" s="21" t="n"/>
       <c r="CH23" s="24">
-        <f>SUM(M23:CF23)</f>
+        <f>H23+SUM(M23:CF23)</f>
         <v/>
       </c>
       <c r="CI23" s="24">
-        <f>I23-CH23</f>
+        <f>I23-H23-SUM(M23:CF23)</f>
         <v/>
       </c>
       <c r="CJ23" s="25">
-        <f>IF(I23=0,"",CH23/I23)</f>
+        <f>IF(I23=0,"",(H23+SUM(M23:CF23))/I23)</f>
         <v/>
       </c>
       <c r="CK23" s="26" t="n"/>
@@ -3733,15 +3768,15 @@
       <c r="CF24" s="21" t="n"/>
       <c r="CG24" s="21" t="n"/>
       <c r="CH24" s="24">
-        <f>SUM(M24:CF24)</f>
+        <f>H24+SUM(M24:CF24)</f>
         <v/>
       </c>
       <c r="CI24" s="24">
-        <f>I24-CH24</f>
+        <f>I24-H24-SUM(M24:CF24)</f>
         <v/>
       </c>
       <c r="CJ24" s="25">
-        <f>IF(I24=0,"",CH24/I24)</f>
+        <f>IF(I24=0,"",(H24+SUM(M24:CF24))/I24)</f>
         <v/>
       </c>
       <c r="CK24" s="26" t="n"/>
@@ -3842,15 +3877,15 @@
       <c r="CF25" s="21" t="n"/>
       <c r="CG25" s="21" t="n"/>
       <c r="CH25" s="24">
-        <f>SUM(M25:CF25)</f>
+        <f>H25+SUM(M25:CF25)</f>
         <v/>
       </c>
       <c r="CI25" s="24">
-        <f>I25-CH25</f>
+        <f>I25-H25-SUM(M25:CF25)</f>
         <v/>
       </c>
       <c r="CJ25" s="25">
-        <f>IF(I25=0,"",CH25/I25)</f>
+        <f>IF(I25=0,"",(H25+SUM(M25:CF25))/I25)</f>
         <v/>
       </c>
       <c r="CK25" s="26" t="n"/>
@@ -3951,15 +3986,15 @@
       <c r="CF26" s="21" t="n"/>
       <c r="CG26" s="21" t="n"/>
       <c r="CH26" s="24">
-        <f>SUM(M26:CF26)</f>
+        <f>H26+SUM(M26:CF26)</f>
         <v/>
       </c>
       <c r="CI26" s="24">
-        <f>I26-CH26</f>
+        <f>I26-H26-SUM(M26:CF26)</f>
         <v/>
       </c>
       <c r="CJ26" s="25">
-        <f>IF(I26=0,"",CH26/I26)</f>
+        <f>IF(I26=0,"",(H26+SUM(M26:CF26))/I26)</f>
         <v/>
       </c>
       <c r="CK26" s="26" t="n"/>
@@ -4060,15 +4095,15 @@
       <c r="CF27" s="21" t="n"/>
       <c r="CG27" s="21" t="n"/>
       <c r="CH27" s="24">
-        <f>SUM(M27:CF27)</f>
+        <f>H27+SUM(M27:CF27)</f>
         <v/>
       </c>
       <c r="CI27" s="24">
-        <f>I27-CH27</f>
+        <f>I27-H27-SUM(M27:CF27)</f>
         <v/>
       </c>
       <c r="CJ27" s="25">
-        <f>IF(I27=0,"",CH27/I27)</f>
+        <f>IF(I27=0,"",(H27+SUM(M27:CF27))/I27)</f>
         <v/>
       </c>
       <c r="CK27" s="26" t="n"/>
@@ -4169,15 +4204,15 @@
       <c r="CF28" s="21" t="n"/>
       <c r="CG28" s="21" t="n"/>
       <c r="CH28" s="24">
-        <f>SUM(M28:CF28)</f>
+        <f>H28+SUM(M28:CF28)</f>
         <v/>
       </c>
       <c r="CI28" s="24">
-        <f>I28-CH28</f>
+        <f>I28-H28-SUM(M28:CF28)</f>
         <v/>
       </c>
       <c r="CJ28" s="25">
-        <f>IF(I28=0,"",CH28/I28)</f>
+        <f>IF(I28=0,"",(H28+SUM(M28:CF28))/I28)</f>
         <v/>
       </c>
       <c r="CK28" s="26" t="n"/>
@@ -4278,15 +4313,15 @@
       <c r="CF29" s="21" t="n"/>
       <c r="CG29" s="21" t="n"/>
       <c r="CH29" s="24">
-        <f>SUM(M29:CF29)</f>
+        <f>H29+SUM(M29:CF29)</f>
         <v/>
       </c>
       <c r="CI29" s="24">
-        <f>I29-CH29</f>
+        <f>I29-H29-SUM(M29:CF29)</f>
         <v/>
       </c>
       <c r="CJ29" s="25">
-        <f>IF(I29=0,"",CH29/I29)</f>
+        <f>IF(I29=0,"",(H29+SUM(M29:CF29))/I29)</f>
         <v/>
       </c>
       <c r="CK29" s="26" t="n"/>
@@ -4387,15 +4422,15 @@
       <c r="CF30" s="21" t="n"/>
       <c r="CG30" s="21" t="n"/>
       <c r="CH30" s="24">
-        <f>SUM(M30:CF30)</f>
+        <f>H30+SUM(M30:CF30)</f>
         <v/>
       </c>
       <c r="CI30" s="24">
-        <f>I30-CH30</f>
+        <f>I30-H30-SUM(M30:CF30)</f>
         <v/>
       </c>
       <c r="CJ30" s="25">
-        <f>IF(I30=0,"",CH30/I30)</f>
+        <f>IF(I30=0,"",(H30+SUM(M30:CF30))/I30)</f>
         <v/>
       </c>
       <c r="CK30" s="26" t="n"/>
@@ -4496,15 +4531,15 @@
       <c r="CF31" s="21" t="n"/>
       <c r="CG31" s="21" t="n"/>
       <c r="CH31" s="24">
-        <f>SUM(M31:CF31)</f>
+        <f>H31+SUM(M31:CF31)</f>
         <v/>
       </c>
       <c r="CI31" s="24">
-        <f>I31-CH31</f>
+        <f>I31-H31-SUM(M31:CF31)</f>
         <v/>
       </c>
       <c r="CJ31" s="25">
-        <f>IF(I31=0,"",CH31/I31)</f>
+        <f>IF(I31=0,"",(H31+SUM(M31:CF31))/I31)</f>
         <v/>
       </c>
       <c r="CK31" s="26" t="n"/>
@@ -4605,15 +4640,15 @@
       <c r="CF32" s="21" t="n"/>
       <c r="CG32" s="21" t="n"/>
       <c r="CH32" s="24">
-        <f>SUM(M32:CF32)</f>
+        <f>H32+SUM(M32:CF32)</f>
         <v/>
       </c>
       <c r="CI32" s="24">
-        <f>I32-CH32</f>
+        <f>I32-H32-SUM(M32:CF32)</f>
         <v/>
       </c>
       <c r="CJ32" s="25">
-        <f>IF(I32=0,"",CH32/I32)</f>
+        <f>IF(I32=0,"",(H32+SUM(M32:CF32))/I32)</f>
         <v/>
       </c>
       <c r="CK32" s="26" t="n"/>
@@ -4714,15 +4749,15 @@
       <c r="CF33" s="21" t="n"/>
       <c r="CG33" s="21" t="n"/>
       <c r="CH33" s="24">
-        <f>SUM(M33:CF33)</f>
+        <f>H33+SUM(M33:CF33)</f>
         <v/>
       </c>
       <c r="CI33" s="24">
-        <f>I33-CH33</f>
+        <f>I33-H33-SUM(M33:CF33)</f>
         <v/>
       </c>
       <c r="CJ33" s="25">
-        <f>IF(I33=0,"",CH33/I33)</f>
+        <f>IF(I33=0,"",(H33+SUM(M33:CF33))/I33)</f>
         <v/>
       </c>
       <c r="CK33" s="26" t="n"/>
@@ -4823,15 +4858,15 @@
       <c r="CF34" s="21" t="n"/>
       <c r="CG34" s="21" t="n"/>
       <c r="CH34" s="24">
-        <f>SUM(M34:CF34)</f>
+        <f>H34+SUM(M34:CF34)</f>
         <v/>
       </c>
       <c r="CI34" s="24">
-        <f>I34-CH34</f>
+        <f>I34-H34-SUM(M34:CF34)</f>
         <v/>
       </c>
       <c r="CJ34" s="25">
-        <f>IF(I34=0,"",CH34/I34)</f>
+        <f>IF(I34=0,"",(H34+SUM(M34:CF34))/I34)</f>
         <v/>
       </c>
       <c r="CK34" s="26" t="n"/>
@@ -4932,15 +4967,15 @@
       <c r="CF35" s="21" t="n"/>
       <c r="CG35" s="21" t="n"/>
       <c r="CH35" s="24">
-        <f>SUM(M35:CF35)</f>
+        <f>H35+SUM(M35:CF35)</f>
         <v/>
       </c>
       <c r="CI35" s="24">
-        <f>I35-CH35</f>
+        <f>I35-H35-SUM(M35:CF35)</f>
         <v/>
       </c>
       <c r="CJ35" s="25">
-        <f>IF(I35=0,"",CH35/I35)</f>
+        <f>IF(I35=0,"",(H35+SUM(M35:CF35))/I35)</f>
         <v/>
       </c>
       <c r="CK35" s="26" t="n"/>
@@ -5041,15 +5076,15 @@
       <c r="CF36" s="21" t="n"/>
       <c r="CG36" s="21" t="n"/>
       <c r="CH36" s="24">
-        <f>SUM(M36:CF36)</f>
+        <f>H36+SUM(M36:CF36)</f>
         <v/>
       </c>
       <c r="CI36" s="24">
-        <f>I36-CH36</f>
+        <f>I36-H36-SUM(M36:CF36)</f>
         <v/>
       </c>
       <c r="CJ36" s="25">
-        <f>IF(I36=0,"",CH36/I36)</f>
+        <f>IF(I36=0,"",(H36+SUM(M36:CF36))/I36)</f>
         <v/>
       </c>
       <c r="CK36" s="26" t="n"/>
@@ -5150,15 +5185,15 @@
       <c r="CF37" s="21" t="n"/>
       <c r="CG37" s="21" t="n"/>
       <c r="CH37" s="24">
-        <f>SUM(M37:CF37)</f>
+        <f>H37+SUM(M37:CF37)</f>
         <v/>
       </c>
       <c r="CI37" s="24">
-        <f>I37-CH37</f>
+        <f>I37-H37-SUM(M37:CF37)</f>
         <v/>
       </c>
       <c r="CJ37" s="25">
-        <f>IF(I37=0,"",CH37/I37)</f>
+        <f>IF(I37=0,"",(H37+SUM(M37:CF37))/I37)</f>
         <v/>
       </c>
       <c r="CK37" s="26" t="n"/>
@@ -5259,15 +5294,15 @@
       <c r="CF38" s="21" t="n"/>
       <c r="CG38" s="21" t="n"/>
       <c r="CH38" s="24">
-        <f>SUM(M38:CF38)</f>
+        <f>H38+SUM(M38:CF38)</f>
         <v/>
       </c>
       <c r="CI38" s="24">
-        <f>I38-CH38</f>
+        <f>I38-H38-SUM(M38:CF38)</f>
         <v/>
       </c>
       <c r="CJ38" s="25">
-        <f>IF(I38=0,"",CH38/I38)</f>
+        <f>IF(I38=0,"",(H38+SUM(M38:CF38))/I38)</f>
         <v/>
       </c>
       <c r="CK38" s="26" t="n"/>
@@ -5368,15 +5403,15 @@
       <c r="CF39" s="21" t="n"/>
       <c r="CG39" s="21" t="n"/>
       <c r="CH39" s="24">
-        <f>SUM(M39:CF39)</f>
+        <f>H39+SUM(M39:CF39)</f>
         <v/>
       </c>
       <c r="CI39" s="24">
-        <f>I39-CH39</f>
+        <f>I39-H39-SUM(M39:CF39)</f>
         <v/>
       </c>
       <c r="CJ39" s="25">
-        <f>IF(I39=0,"",CH39/I39)</f>
+        <f>IF(I39=0,"",(H39+SUM(M39:CF39))/I39)</f>
         <v/>
       </c>
       <c r="CK39" s="26" t="n"/>
@@ -5477,15 +5512,15 @@
       <c r="CF40" s="21" t="n"/>
       <c r="CG40" s="21" t="n"/>
       <c r="CH40" s="24">
-        <f>SUM(M40:CF40)</f>
+        <f>H40+SUM(M40:CF40)</f>
         <v/>
       </c>
       <c r="CI40" s="24">
-        <f>I40-CH40</f>
+        <f>I40-H40-SUM(M40:CF40)</f>
         <v/>
       </c>
       <c r="CJ40" s="25">
-        <f>IF(I40=0,"",CH40/I40)</f>
+        <f>IF(I40=0,"",(H40+SUM(M40:CF40))/I40)</f>
         <v/>
       </c>
       <c r="CK40" s="26" t="n"/>
@@ -5586,15 +5621,15 @@
       <c r="CF41" s="21" t="n"/>
       <c r="CG41" s="21" t="n"/>
       <c r="CH41" s="24">
-        <f>SUM(M41:CF41)</f>
+        <f>H41+SUM(M41:CF41)</f>
         <v/>
       </c>
       <c r="CI41" s="24">
-        <f>I41-CH41</f>
+        <f>I41-H41-SUM(M41:CF41)</f>
         <v/>
       </c>
       <c r="CJ41" s="25">
-        <f>IF(I41=0,"",CH41/I41)</f>
+        <f>IF(I41=0,"",(H41+SUM(M41:CF41))/I41)</f>
         <v/>
       </c>
       <c r="CK41" s="26" t="n"/>
@@ -5695,15 +5730,15 @@
       <c r="CF42" s="21" t="n"/>
       <c r="CG42" s="21" t="n"/>
       <c r="CH42" s="24">
-        <f>SUM(M42:CF42)</f>
+        <f>H42+SUM(M42:CF42)</f>
         <v/>
       </c>
       <c r="CI42" s="24">
-        <f>I42-CH42</f>
+        <f>I42-H42-SUM(M42:CF42)</f>
         <v/>
       </c>
       <c r="CJ42" s="25">
-        <f>IF(I42=0,"",CH42/I42)</f>
+        <f>IF(I42=0,"",(H42+SUM(M42:CF42))/I42)</f>
         <v/>
       </c>
       <c r="CK42" s="26" t="n"/>
@@ -5804,15 +5839,15 @@
       <c r="CF43" s="21" t="n"/>
       <c r="CG43" s="21" t="n"/>
       <c r="CH43" s="24">
-        <f>SUM(M43:CF43)</f>
+        <f>H43+SUM(M43:CF43)</f>
         <v/>
       </c>
       <c r="CI43" s="24">
-        <f>I43-CH43</f>
+        <f>I43-H43-SUM(M43:CF43)</f>
         <v/>
       </c>
       <c r="CJ43" s="25">
-        <f>IF(I43=0,"",CH43/I43)</f>
+        <f>IF(I43=0,"",(H43+SUM(M43:CF43))/I43)</f>
         <v/>
       </c>
       <c r="CK43" s="26" t="n"/>
@@ -5913,15 +5948,15 @@
       <c r="CF44" s="21" t="n"/>
       <c r="CG44" s="21" t="n"/>
       <c r="CH44" s="24">
-        <f>SUM(M44:CF44)</f>
+        <f>H44+SUM(M44:CF44)</f>
         <v/>
       </c>
       <c r="CI44" s="24">
-        <f>I44-CH44</f>
+        <f>I44-H44-SUM(M44:CF44)</f>
         <v/>
       </c>
       <c r="CJ44" s="25">
-        <f>IF(I44=0,"",CH44/I44)</f>
+        <f>IF(I44=0,"",(H44+SUM(M44:CF44))/I44)</f>
         <v/>
       </c>
       <c r="CK44" s="26" t="n"/>
@@ -6022,15 +6057,15 @@
       <c r="CF45" s="21" t="n"/>
       <c r="CG45" s="21" t="n"/>
       <c r="CH45" s="24">
-        <f>SUM(M45:CF45)</f>
+        <f>H45+SUM(M45:CF45)</f>
         <v/>
       </c>
       <c r="CI45" s="24">
-        <f>I45-CH45</f>
+        <f>I45-H45-SUM(M45:CF45)</f>
         <v/>
       </c>
       <c r="CJ45" s="25">
-        <f>IF(I45=0,"",CH45/I45)</f>
+        <f>IF(I45=0,"",(H45+SUM(M45:CF45))/I45)</f>
         <v/>
       </c>
       <c r="CK45" s="26" t="n"/>
@@ -6131,15 +6166,15 @@
       <c r="CF46" s="21" t="n"/>
       <c r="CG46" s="21" t="n"/>
       <c r="CH46" s="24">
-        <f>SUM(M46:CF46)</f>
+        <f>H46+SUM(M46:CF46)</f>
         <v/>
       </c>
       <c r="CI46" s="24">
-        <f>I46-CH46</f>
+        <f>I46-H46-SUM(M46:CF46)</f>
         <v/>
       </c>
       <c r="CJ46" s="25">
-        <f>IF(I46=0,"",CH46/I46)</f>
+        <f>IF(I46=0,"",(H46+SUM(M46:CF46))/I46)</f>
         <v/>
       </c>
       <c r="CK46" s="26" t="n"/>
@@ -6240,15 +6275,15 @@
       <c r="CF47" s="21" t="n"/>
       <c r="CG47" s="21" t="n"/>
       <c r="CH47" s="24">
-        <f>SUM(M47:CF47)</f>
+        <f>H47+SUM(M47:CF47)</f>
         <v/>
       </c>
       <c r="CI47" s="24">
-        <f>I47-CH47</f>
+        <f>I47-H47-SUM(M47:CF47)</f>
         <v/>
       </c>
       <c r="CJ47" s="25">
-        <f>IF(I47=0,"",CH47/I47)</f>
+        <f>IF(I47=0,"",(H47+SUM(M47:CF47))/I47)</f>
         <v/>
       </c>
       <c r="CK47" s="26" t="n"/>
@@ -6349,15 +6384,15 @@
       <c r="CF48" s="21" t="n"/>
       <c r="CG48" s="21" t="n"/>
       <c r="CH48" s="24">
-        <f>SUM(M48:CF48)</f>
+        <f>H48+SUM(M48:CF48)</f>
         <v/>
       </c>
       <c r="CI48" s="24">
-        <f>I48-CH48</f>
+        <f>I48-H48-SUM(M48:CF48)</f>
         <v/>
       </c>
       <c r="CJ48" s="25">
-        <f>IF(I48=0,"",CH48/I48)</f>
+        <f>IF(I48=0,"",(H48+SUM(M48:CF48))/I48)</f>
         <v/>
       </c>
       <c r="CK48" s="26" t="n"/>
@@ -6458,15 +6493,15 @@
       <c r="CF49" s="21" t="n"/>
       <c r="CG49" s="21" t="n"/>
       <c r="CH49" s="24">
-        <f>SUM(M49:CF49)</f>
+        <f>H49+SUM(M49:CF49)</f>
         <v/>
       </c>
       <c r="CI49" s="24">
-        <f>I49-CH49</f>
+        <f>I49-H49-SUM(M49:CF49)</f>
         <v/>
       </c>
       <c r="CJ49" s="25">
-        <f>IF(I49=0,"",CH49/I49)</f>
+        <f>IF(I49=0,"",(H49+SUM(M49:CF49))/I49)</f>
         <v/>
       </c>
       <c r="CK49" s="26" t="n"/>
@@ -6567,15 +6602,15 @@
       <c r="CF50" s="21" t="n"/>
       <c r="CG50" s="21" t="n"/>
       <c r="CH50" s="24">
-        <f>SUM(M50:CF50)</f>
+        <f>H50+SUM(M50:CF50)</f>
         <v/>
       </c>
       <c r="CI50" s="24">
-        <f>I50-CH50</f>
+        <f>I50-H50-SUM(M50:CF50)</f>
         <v/>
       </c>
       <c r="CJ50" s="25">
-        <f>IF(I50=0,"",CH50/I50)</f>
+        <f>IF(I50=0,"",(H50+SUM(M50:CF50))/I50)</f>
         <v/>
       </c>
       <c r="CK50" s="26" t="n"/>
@@ -6676,15 +6711,15 @@
       <c r="CF51" s="21" t="n"/>
       <c r="CG51" s="21" t="n"/>
       <c r="CH51" s="24">
-        <f>SUM(M51:CF51)</f>
+        <f>H51+SUM(M51:CF51)</f>
         <v/>
       </c>
       <c r="CI51" s="24">
-        <f>I51-CH51</f>
+        <f>I51-H51-SUM(M51:CF51)</f>
         <v/>
       </c>
       <c r="CJ51" s="25">
-        <f>IF(I51=0,"",CH51/I51)</f>
+        <f>IF(I51=0,"",(H51+SUM(M51:CF51))/I51)</f>
         <v/>
       </c>
       <c r="CK51" s="26" t="n"/>
